--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H637"/>
+  <dimension ref="A1:H640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19548,6 +19548,96 @@
         <v>315.53</v>
       </c>
       <c r="H637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>318.2</v>
+      </c>
+      <c r="C638" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="D638" t="n">
+        <v>320.19</v>
+      </c>
+      <c r="E638" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="F638" t="n">
+        <v>310.51</v>
+      </c>
+      <c r="G638" t="n">
+        <v>315.78</v>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>317.83</v>
+      </c>
+      <c r="C639" t="n">
+        <v>313.53</v>
+      </c>
+      <c r="D639" t="n">
+        <v>319.98</v>
+      </c>
+      <c r="E639" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="F639" t="n">
+        <v>310.42</v>
+      </c>
+      <c r="G639" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="C640" t="n">
+        <v>313.87</v>
+      </c>
+      <c r="D640" t="n">
+        <v>319.91</v>
+      </c>
+      <c r="E640" t="n">
+        <v>322.48</v>
+      </c>
+      <c r="F640" t="n">
+        <v>310.82</v>
+      </c>
+      <c r="G640" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="H640" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19564,7 +19654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B747"/>
+  <dimension ref="A1:B750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27037,6 +27127,36 @@
       </c>
       <c r="B747" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -27205,28 +27325,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03248125203386709</v>
+        <v>-0.03666993620325102</v>
       </c>
       <c r="J2" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K2" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002770981792847294</v>
+        <v>0.003545481709331111</v>
       </c>
       <c r="M2" t="n">
-        <v>3.465598348002906</v>
+        <v>3.470519621768136</v>
       </c>
       <c r="N2" t="n">
-        <v>17.48707929626762</v>
+        <v>17.49004564974654</v>
       </c>
       <c r="O2" t="n">
-        <v>4.181755528036954</v>
+        <v>4.182110191009623</v>
       </c>
       <c r="P2" t="n">
-        <v>323.0110525880287</v>
+        <v>323.0631723611791</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27287,28 +27407,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3504730147368013</v>
+        <v>-0.3508207339111206</v>
       </c>
       <c r="J3" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K3" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4792779890733821</v>
+        <v>0.4821260256598485</v>
       </c>
       <c r="M3" t="n">
-        <v>1.918338029107429</v>
+        <v>1.91092063519055</v>
       </c>
       <c r="N3" t="n">
-        <v>6.146362087986691</v>
+        <v>6.118182375546152</v>
       </c>
       <c r="O3" t="n">
-        <v>2.479185771173006</v>
+        <v>2.473495982520722</v>
       </c>
       <c r="P3" t="n">
-        <v>323.4641748041134</v>
+        <v>323.4685011758208</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27369,28 +27489,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1613507870335049</v>
+        <v>-0.162123357588285</v>
       </c>
       <c r="J4" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K4" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1838162809127442</v>
+        <v>0.1866132424652805</v>
       </c>
       <c r="M4" t="n">
-        <v>1.774564650641058</v>
+        <v>1.770196972009945</v>
       </c>
       <c r="N4" t="n">
-        <v>5.323982877873939</v>
+        <v>5.301932815367959</v>
       </c>
       <c r="O4" t="n">
-        <v>2.307375755674385</v>
+        <v>2.302592629052729</v>
       </c>
       <c r="P4" t="n">
-        <v>325.1534508624437</v>
+        <v>325.163064276619</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27451,28 +27571,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2710815516101833</v>
+        <v>-0.2718958946715008</v>
       </c>
       <c r="J5" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K5" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3642236500713004</v>
+        <v>0.3677000353375414</v>
       </c>
       <c r="M5" t="n">
-        <v>1.854114895500312</v>
+        <v>1.848693786064798</v>
       </c>
       <c r="N5" t="n">
-        <v>5.907812090343333</v>
+        <v>5.883329732336059</v>
       </c>
       <c r="O5" t="n">
-        <v>2.43059912168653</v>
+        <v>2.425557612660656</v>
       </c>
       <c r="P5" t="n">
-        <v>330.5909758909061</v>
+        <v>330.6011089070527</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27533,28 +27653,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2865595268807867</v>
+        <v>-0.2920195068120284</v>
       </c>
       <c r="J6" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K6" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3371113254626501</v>
+        <v>0.3433968372693036</v>
       </c>
       <c r="M6" t="n">
-        <v>2.161259848867253</v>
+        <v>2.174001351557991</v>
       </c>
       <c r="N6" t="n">
-        <v>7.436823601369188</v>
+        <v>7.546034881593219</v>
       </c>
       <c r="O6" t="n">
-        <v>2.72705401511763</v>
+        <v>2.747004710879328</v>
       </c>
       <c r="P6" t="n">
-        <v>323.8672765261416</v>
+        <v>323.9352131090794</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27615,28 +27735,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1735244085401743</v>
+        <v>-0.1798170023456571</v>
       </c>
       <c r="J7" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="K7" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09626942483726331</v>
+        <v>0.1021779370740211</v>
       </c>
       <c r="M7" t="n">
-        <v>2.912460659000784</v>
+        <v>2.928314662103686</v>
       </c>
       <c r="N7" t="n">
-        <v>13.01853950968</v>
+        <v>13.14870715144094</v>
       </c>
       <c r="O7" t="n">
-        <v>3.608121326906844</v>
+        <v>3.626114608150291</v>
       </c>
       <c r="P7" t="n">
-        <v>326.8471520826901</v>
+        <v>326.9254490130202</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27678,7 +27798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H637"/>
+  <dimension ref="A1:H640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54435,6 +54555,132 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-45.16653091756584,170.91039898593286</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-45.16692959586535,170.90967242835248</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-45.16746705492828,170.90915949386698</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-45.1679565321178,170.90856775344403</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-45.16843720642925,170.90795815185257</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-45.16896406198753,170.9074886596697</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-45.16652838392565,170.91039593231085</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-45.16692883505886,170.909671345085</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-45.1674657970179,170.90915750034424</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-45.16795508411248,170.90856515554745</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-45.16843673891116,170.90795721698723</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-45.168963240946354,170.90748714509766</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-45.166526466576286,170.91039362146194</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-45.16693099067721,170.909674414343</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-45.16746537771443,170.90915683583668</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-45.16795586380765,170.90856655441485</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-45.168438816769346,170.90796137194437</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-45.168964499876154,170.90748946744145</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H640"/>
+  <dimension ref="A1:H645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19638,6 +19638,156 @@
         <v>315.86</v>
       </c>
       <c r="H640" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:13:47+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>317.54</v>
+      </c>
+      <c r="C641" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="D641" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="E641" t="n">
+        <v>322.06</v>
+      </c>
+      <c r="F641" t="n">
+        <v>310.55</v>
+      </c>
+      <c r="G641" t="n">
+        <v>315.69</v>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>317.04</v>
+      </c>
+      <c r="C642" t="n">
+        <v>312.52</v>
+      </c>
+      <c r="D642" t="n">
+        <v>318.82</v>
+      </c>
+      <c r="E642" t="n">
+        <v>321.03</v>
+      </c>
+      <c r="F642" t="n">
+        <v>309.78</v>
+      </c>
+      <c r="G642" t="n">
+        <v>314.97</v>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>317.15</v>
+      </c>
+      <c r="C643" t="n">
+        <v>312.16</v>
+      </c>
+      <c r="D643" t="n">
+        <v>318.83</v>
+      </c>
+      <c r="E643" t="n">
+        <v>321.06</v>
+      </c>
+      <c r="F643" t="n">
+        <v>310.02</v>
+      </c>
+      <c r="G643" t="n">
+        <v>314.85</v>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>317.78</v>
+      </c>
+      <c r="C644" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="D644" t="n">
+        <v>318.48</v>
+      </c>
+      <c r="E644" t="n">
+        <v>319.95</v>
+      </c>
+      <c r="F644" t="n">
+        <v>309.06</v>
+      </c>
+      <c r="G644" t="n">
+        <v>314.94</v>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>317.9</v>
+      </c>
+      <c r="C645" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="D645" t="n">
+        <v>318.37</v>
+      </c>
+      <c r="E645" t="n">
+        <v>320.05</v>
+      </c>
+      <c r="F645" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="G645" t="n">
+        <v>315.12</v>
+      </c>
+      <c r="H645" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19654,7 +19804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B750"/>
+  <dimension ref="A1:B756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27157,6 +27307,66 @@
       </c>
       <c r="B750" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -27325,28 +27535,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03666993620325102</v>
+        <v>-0.0440400757674726</v>
       </c>
       <c r="J2" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="K2" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003545481709331111</v>
+        <v>0.005138857731589841</v>
       </c>
       <c r="M2" t="n">
-        <v>3.470519621768136</v>
+        <v>3.480734185188082</v>
       </c>
       <c r="N2" t="n">
-        <v>17.49004564974654</v>
+        <v>17.51525714803812</v>
       </c>
       <c r="O2" t="n">
-        <v>4.182110191009623</v>
+        <v>4.185123313361044</v>
       </c>
       <c r="P2" t="n">
-        <v>323.0631723611791</v>
+        <v>323.1551050098516</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27407,28 +27617,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3508207339111206</v>
+        <v>-0.3532074363346759</v>
       </c>
       <c r="J3" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="K3" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4821260256598485</v>
+        <v>0.4886737738728434</v>
       </c>
       <c r="M3" t="n">
-        <v>1.91092063519055</v>
+        <v>1.906906694339352</v>
       </c>
       <c r="N3" t="n">
-        <v>6.118182375546152</v>
+        <v>6.089242115753719</v>
       </c>
       <c r="O3" t="n">
-        <v>2.473495982520722</v>
+        <v>2.467638975975562</v>
       </c>
       <c r="P3" t="n">
-        <v>323.4685011758208</v>
+        <v>323.4982805857923</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27489,28 +27699,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.162123357588285</v>
+        <v>-0.1652992322872328</v>
       </c>
       <c r="J4" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="K4" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866132424652805</v>
+        <v>0.1941059019594026</v>
       </c>
       <c r="M4" t="n">
-        <v>1.770196972009945</v>
+        <v>1.772776297974896</v>
       </c>
       <c r="N4" t="n">
-        <v>5.301932815367959</v>
+        <v>5.291824547928366</v>
       </c>
       <c r="O4" t="n">
-        <v>2.302592629052729</v>
+        <v>2.300396606659027</v>
       </c>
       <c r="P4" t="n">
-        <v>325.163064276619</v>
+        <v>325.2026891888416</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27571,28 +27781,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2718958946715008</v>
+        <v>-0.2758179495822772</v>
       </c>
       <c r="J5" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="K5" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3677000353375414</v>
+        <v>0.3760751286924233</v>
       </c>
       <c r="M5" t="n">
-        <v>1.848693786064798</v>
+        <v>1.849966113764657</v>
       </c>
       <c r="N5" t="n">
-        <v>5.883329732336059</v>
+        <v>5.887450456423995</v>
       </c>
       <c r="O5" t="n">
-        <v>2.425557612660656</v>
+        <v>2.426406902484411</v>
       </c>
       <c r="P5" t="n">
-        <v>330.6011089070527</v>
+        <v>330.6500495384021</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27653,28 +27863,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2920195068120284</v>
+        <v>-0.3020985820270829</v>
       </c>
       <c r="J6" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="K6" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3433968372693036</v>
+        <v>0.3534173060409355</v>
       </c>
       <c r="M6" t="n">
-        <v>2.174001351557991</v>
+        <v>2.201173406234339</v>
       </c>
       <c r="N6" t="n">
-        <v>7.546034881593219</v>
+        <v>7.788577879261306</v>
       </c>
       <c r="O6" t="n">
-        <v>2.747004710879328</v>
+        <v>2.790802371946338</v>
       </c>
       <c r="P6" t="n">
-        <v>323.9352131090794</v>
+        <v>324.0609522247951</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27735,28 +27945,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1798170023456571</v>
+        <v>-0.1909912362981177</v>
       </c>
       <c r="J7" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="K7" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1021779370740211</v>
+        <v>0.1125620215875792</v>
       </c>
       <c r="M7" t="n">
-        <v>2.928314662103686</v>
+        <v>2.958358300682919</v>
       </c>
       <c r="N7" t="n">
-        <v>13.14870715144094</v>
+        <v>13.41521184493976</v>
       </c>
       <c r="O7" t="n">
-        <v>3.626114608150291</v>
+        <v>3.662678233880198</v>
       </c>
       <c r="P7" t="n">
-        <v>326.9254490130202</v>
+        <v>327.0648431659853</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27798,7 +28008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H640"/>
+  <dimension ref="A1:H645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54681,6 +54891,216 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:13:47+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-45.16652639809952,170.9103935389316</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-45.16692832785453,170.90967062290667</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-45.16746340099802,170.90915370315835</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-45.167953524722066,170.9085623578128</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-45.168437414215084,170.9079585673483</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-45.16896356936282,170.90748775092646</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-45.16652297426123,170.9103894124161</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-45.16692243160388,170.90966222758462</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-45.1674588485599,170.90914648850602</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-45.16794778839249,170.9085520661474</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-45.16843341433774,170.90795056905642</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-45.168959628364895,170.9074804809812</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-45.16652372750567,170.9103903202495</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-45.16692014918413,170.90965897778298</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-45.167458908460404,170.90914658343564</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-45.167947955470055,170.9085523659046</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-45.16843466105282,170.90795306203037</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-45.16895897153187,170.90747926932374</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-45.166528041541845,170.91039551965923</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-45.16692167079731,170.90966114431737</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-45.167456811942714,170.90914326089876</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-45.16794177359936,170.90854127488882</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-45.16842967419222,170.90794309013523</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-45.16895946415665,170.90748017806683</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-45.166528863263,170.91039651002308</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-45.16691976878082,170.9096584361494</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-45.16745615303713,170.90914221667293</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-45.167942330524696,170.90854227407934</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-45.16843195983675,170.90794766058696</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-45.16896044940618,170.90748199555304</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0475/nzd0475.xlsx
+++ b/data/nzd0475/nzd0475.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H645"/>
+  <dimension ref="A1:H648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19788,6 +19788,96 @@
         <v>315.12</v>
       </c>
       <c r="H645" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:13+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>318.03</v>
+      </c>
+      <c r="C646" t="n">
+        <v>311.66</v>
+      </c>
+      <c r="D646" t="n">
+        <v>318.28</v>
+      </c>
+      <c r="E646" t="n">
+        <v>319.74</v>
+      </c>
+      <c r="F646" t="n">
+        <v>308.92</v>
+      </c>
+      <c r="G646" t="n">
+        <v>314.46</v>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>318.31</v>
+      </c>
+      <c r="C647" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="D647" t="n">
+        <v>318.11</v>
+      </c>
+      <c r="E647" t="n">
+        <v>319.82</v>
+      </c>
+      <c r="F647" t="n">
+        <v>308.73</v>
+      </c>
+      <c r="G647" t="n">
+        <v>314.27</v>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>317.73</v>
+      </c>
+      <c r="C648" t="n">
+        <v>311.74</v>
+      </c>
+      <c r="D648" t="n">
+        <v>317.78</v>
+      </c>
+      <c r="E648" t="n">
+        <v>319.58</v>
+      </c>
+      <c r="F648" t="n">
+        <v>309.26</v>
+      </c>
+      <c r="G648" t="n">
+        <v>313.75</v>
+      </c>
+      <c r="H648" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19804,7 +19894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B756"/>
+  <dimension ref="A1:B759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27367,6 +27457,36 @@
       </c>
       <c r="B756" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -27535,28 +27655,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0440400757674726</v>
+        <v>-0.0478201218900345</v>
       </c>
       <c r="J2" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K2" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005138857731589841</v>
+        <v>0.006085214531269201</v>
       </c>
       <c r="M2" t="n">
-        <v>3.480734185188082</v>
+        <v>3.483532668766519</v>
       </c>
       <c r="N2" t="n">
-        <v>17.51525714803812</v>
+        <v>17.50540082539002</v>
       </c>
       <c r="O2" t="n">
-        <v>4.185123313361044</v>
+        <v>4.183945604975048</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1551050098516</v>
+        <v>323.2024394988912</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27617,28 +27737,28 @@
         <v>0.1987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3532074363346759</v>
+        <v>-0.355089288151992</v>
       </c>
       <c r="J3" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K3" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4886737738728434</v>
+        <v>0.4929171056964652</v>
       </c>
       <c r="M3" t="n">
-        <v>1.906906694339352</v>
+        <v>1.906574006812515</v>
       </c>
       <c r="N3" t="n">
-        <v>6.089242115753719</v>
+        <v>6.079357144435057</v>
       </c>
       <c r="O3" t="n">
-        <v>2.467638975975562</v>
+        <v>2.465635241562518</v>
       </c>
       <c r="P3" t="n">
-        <v>323.4982805857923</v>
+        <v>323.5218446861724</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27699,28 +27819,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1652992322872328</v>
+        <v>-0.1678631369401234</v>
       </c>
       <c r="J4" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K4" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1941059019594026</v>
+        <v>0.1994691032981856</v>
       </c>
       <c r="M4" t="n">
-        <v>1.772776297974896</v>
+        <v>1.777633570141175</v>
       </c>
       <c r="N4" t="n">
-        <v>5.291824547928366</v>
+        <v>5.30017948411246</v>
       </c>
       <c r="O4" t="n">
-        <v>2.300396606659027</v>
+        <v>2.302211867772482</v>
       </c>
       <c r="P4" t="n">
-        <v>325.2026891888416</v>
+        <v>325.2347959394555</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27781,28 +27901,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2758179495822772</v>
+        <v>-0.2791485942000502</v>
       </c>
       <c r="J5" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K5" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3760751286924233</v>
+        <v>0.3817227991726782</v>
       </c>
       <c r="M5" t="n">
-        <v>1.849966113764657</v>
+        <v>1.85450398186299</v>
       </c>
       <c r="N5" t="n">
-        <v>5.887450456423995</v>
+        <v>5.915391141609914</v>
       </c>
       <c r="O5" t="n">
-        <v>2.426406902484411</v>
+        <v>2.432157713144835</v>
       </c>
       <c r="P5" t="n">
-        <v>330.6500495384021</v>
+        <v>330.6917560832608</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27863,28 +27983,28 @@
         <v>0.077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3020985820270829</v>
+        <v>-0.3087287490750786</v>
       </c>
       <c r="J6" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K6" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3534173060409355</v>
+        <v>0.3591363030597138</v>
       </c>
       <c r="M6" t="n">
-        <v>2.201173406234339</v>
+        <v>2.221066791880946</v>
       </c>
       <c r="N6" t="n">
-        <v>7.788577879261306</v>
+        <v>7.971461516013492</v>
       </c>
       <c r="O6" t="n">
-        <v>2.790802371946338</v>
+        <v>2.823377678599428</v>
       </c>
       <c r="P6" t="n">
-        <v>324.0609522247951</v>
+        <v>324.1439730700641</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27945,28 +28065,28 @@
         <v>0.1747</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1909912362981177</v>
+        <v>-0.1984121310936529</v>
       </c>
       <c r="J7" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="K7" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1125620215875792</v>
+        <v>0.1192488199655688</v>
       </c>
       <c r="M7" t="n">
-        <v>2.958358300682919</v>
+        <v>2.979794184599362</v>
       </c>
       <c r="N7" t="n">
-        <v>13.41521184493976</v>
+        <v>13.62740086732216</v>
       </c>
       <c r="O7" t="n">
-        <v>3.662678233880198</v>
+        <v>3.691530965239512</v>
       </c>
       <c r="P7" t="n">
-        <v>327.0648431659853</v>
+        <v>327.1577693934208</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28008,7 +28128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H645"/>
+  <dimension ref="A1:H648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55101,6 +55221,132 @@
         </is>
       </c>
     </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:13+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-45.1665297534609,170.91039758291728</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-45.16691697915651,170.90965446417007</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-45.16745561393255,170.90914136230637</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-45.16794060405613,170.9085391765888</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-45.16842894694164,170.90794163590064</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-45.16895683682444,170.90747533143724</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-45.1665316708102,170.91039989376645</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-45.16692255840498,170.90966240812915</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-45.1674545956239,170.9091397485029</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-45.167941049596415,170.90853997594118</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-45.168427959958684,170.90793966229666</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-45.16895579683872,170.9074734129798</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-45.16652769915804,170.91039510700764</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-45.166917486360944,170.9096551863481</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-45.16745261890705,170.90913661582573</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-45.16793971297555,170.9085375778841</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-45.16843071312157,170.90794516761324</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-45.16895295056186,170.9074681624651</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
